--- a/Chapter_13/13.1_AI_Types_Architectural_Threats.xlsx
+++ b/Chapter_13/13.1_AI_Types_Architectural_Threats.xlsx
@@ -1,184 +1,182 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Types &amp; Threats" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AI Types &amp; Threats" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t xml:space="preserve">AI Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Architectural Threats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Learning (ML)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learns statistical patterns from large datasets to make predictions or classifications on new, unseen data. Encompasses decision trees, support vector machines, random forests, and regression models.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data poisoning (corrupting training data); model extraction (stealing learned parameters via repeated queries); adversarial inputs (causing misclassification); membership inference (revealing whether a record was in training data); model inversion (reconstructing sensitive training data from outputs).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-layer artificial neural networks (CNNs, RNNs, and successors) that model complex, nonlinear relationships and enabled the breakthroughs in image recognition, speech processing, and natural language understanding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inherits every ML threat above and adds: adversarial examples with imperceptible perturbations (including physical-world variants such as adversarial patches on stop signs); backdoor and trojan attacks via poisoned training; query-based extraction amplified by gradient leakage in confidence scores; opacity-driven detection failure where benign drift, poisoning, backdoors, and adversarial inputs cannot be distinguished from the model itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large Language Models (LLMs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning models trained on vast text corpora to predict the next token in a sequence. Examples include OpenAI's GPT, Anthropic's Claude, Google's Gemini, and Meta's Llama.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct and indirect prompt injection; hallucination and confidently fabricated outputs; instruction/data boundary blur intrinsic to natural language processing; sensitive training data leakage; system prompt extraction; jailbreaks that bypass behavioral guardrails.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative AI (GenAI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The broader category of AI systems that create new content (text, images, audio, video, code) rather than merely classifying or predicting. Includes LLMs for text, diffusion models for images, and GANs for visual and multimedia content.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deepfakes used for social engineering and executive impersonation; AI-generated malware and phishing at scale; synthetic media for fraud and disinformation; intellectual property and confidential data leakage through generated outputs; AI-assisted copyright and licensing risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentic AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autonomous systems that reason about goals, decompose tasks, invoke external tools (APIs, databases, code interpreters, browsers), maintain memory across interactions, and take actions in enterprise infrastructure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal hijacking via prompt injection (direct and indirect); tool misuse and privilege escalation; context and memory poisoning; agent-to-agent propagation in multi-agent meshes; identity impersonation through agent-held credentials and tokens; transformation of the security surface from content risk to operational risk.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4">
     <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color indexed="65"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="2" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="3" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -224,13 +222,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -258,13 +256,13 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -461,125 +459,309 @@
 </a:theme>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col customWidth="1" min="1" max="1" width="26"/>
+    <col customWidth="1" min="2" max="2" width="50"/>
+    <col customWidth="1" min="3" max="3" width="70"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AI Type</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Primary Function</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Primary Architectural Threats</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="110" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Machine Learning (ML)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Learns statistical patterns from large datasets to make predictions or classifications on new, unseen data. Encompasses decision trees, support vector machines, random forests, and regression models.</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Data poisoning (corrupting training data); model extraction (stealing learned parameters via repeated queries); adversarial inputs (causing misclassification); membership inference (revealing whether a record was in training data); model inversion (reconstructing sensitive training data from outputs).</t>
-        </is>
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="110" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Deep Learning</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Multi-layer artificial neural networks (CNNs, RNNs, and successors) that model complex, nonlinear relationships and enabled the breakthroughs in image recognition, speech processing, and natural language understanding.</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Inherits every ML threat above and adds: adversarial examples with imperceptible perturbations (including physical-world variants such as adversarial patches on stop signs); backdoor and trojan attacks via poisoned training; query-based extraction amplified by gradient leakage in confidence scores; opacity-driven detection failure where benign drift, poisoning, backdoors, and adversarial inputs cannot be distinguished from the model itself.</t>
-        </is>
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="110" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Large Language Models (LLMs)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Transformer-based deep learning models trained on vast text corpora to predict the next token in a sequence. Examples include OpenAI's GPT, Anthropic's Claude, Google's Gemini, and Meta's Llama.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Direct and indirect prompt injection; hallucination and confidently fabricated outputs; instruction/data boundary blur intrinsic to natural language processing; sensitive training data leakage; system prompt extraction; jailbreaks that bypass behavioral guardrails.</t>
-        </is>
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="110" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Generative AI (GenAI)</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>The broader category of AI systems that create new content (text, images, audio, video, code) rather than merely classifying or predicting. Includes LLMs for text, diffusion models for images, and GANs for visual and multimedia content.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Deepfakes used for social engineering and executive impersonation; AI-generated malware and phishing at scale; synthetic media for fraud and disinformation; intellectual property and confidential data leakage through generated outputs; AI-assisted copyright and licensing risk.</t>
-        </is>
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Agentic AI</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Autonomous systems that reason about goals, decompose tasks, invoke external tools (APIs, databases, code interpreters, browsers), maintain memory across interactions, and take actions in enterprise infrastructure.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Goal hijacking via prompt injection (direct and indirect); tool misuse and privilege escalation; context and memory poisoning; agent-to-agent propagation in multi-agent meshes; identity impersonation through agent-held credentials and tokens; transformation of the security surface from content risk to operational risk.</t>
-        </is>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="1"/>
+  <printOptions headings="0" gridLines="0" horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>